--- a/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
+++ b/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\Sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD82BEC-EFEF-43BA-96A7-6A4A32A8ED13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261362C4-DC27-4088-B60E-72B5A781F460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="1" activeTab="8" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -581,7 +581,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -641,7 +641,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,11 +676,11 @@
       <sheetName val="Wagon"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="8">
@@ -689,7 +689,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1012,13 +1012,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AE9BB5-1866-604F-9CDF-A9F9C66D7CCC}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1037,8 +1037,12 @@
         <f>"INSERT INTO StationType (id, description) VALUES (1, 'Freight yards');"</f>
         <v>INSERT INTO StationType (id, description) VALUES (1, 'Freight yards');</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M2" t="str">
+        <f>"INSERT INTO AreaType (id, name) VALUES (1, 'warehouse');"</f>
+        <v>INSERT INTO AreaType (id, name) VALUES (1, 'warehouse');</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1049,8 +1053,12 @@
         <f>"INSERT INTO StationType (id, description) VALUES (2, 'Stations');"</f>
         <v>INSERT INTO StationType (id, description) VALUES (2, 'Stations');</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M3" t="str">
+        <f>"INSERT INTO AreaType (id, name) VALUES (2, 'refrigerated area');"</f>
+        <v>INSERT INTO AreaType (id, name) VALUES (2, 'refrigerated area');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1061,8 +1069,12 @@
         <f>"INSERT INTO StationType (id, description) VALUES (3, 'Terminals');"</f>
         <v>INSERT INTO StationType (id, description) VALUES (3, 'Terminals');</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M4" t="str">
+        <f>"INSERT INTO AreaType (id, name) VALUES (3, 'grain silo');"</f>
+        <v>INSERT INTO AreaType (id, name) VALUES (3, 'grain silo');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1070,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1082,7 +1094,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (1, 'São Romão',1);</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1090,11 +1102,15 @@
         <v>7</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" ref="E7:E33" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A3&amp;", '"&amp;B3&amp;"',1);"</f>
+        <f t="shared" ref="E7:E32" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A3&amp;", '"&amp;B3&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (2, 'Tamel',1);</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M7" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,2);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,2);</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1105,8 +1121,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (3, 'Senhora das Dores',1);</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="R8" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,3);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,3);</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1118,7 +1138,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (4, 'Lousado',1);</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1129,8 +1149,16 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (5, 'Porto Campanhã',1);</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M10" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,5);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,5);</v>
+      </c>
+      <c r="R10" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,5);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,5);</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1141,8 +1169,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (6, 'Leandro',1);</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="W11" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,6);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,6);</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1153,8 +1185,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (7, 'Porto São Bento',1);</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="R12" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,7);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,7);</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1166,7 +1202,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (8, 'Barcelos',1);</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1177,8 +1213,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (9, 'Vila Nova da Cerveira',1);</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M14" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,9);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,9);</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1190,7 +1230,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (10, 'Midões',1);</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1201,8 +1241,20 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (11, 'Valença',1);</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M16" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,11);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,11);</v>
+      </c>
+      <c r="R16" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,11);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,11);</v>
+      </c>
+      <c r="W16" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,11);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,11);</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1213,8 +1265,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (12, 'Darque',1);</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="R17" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,12);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,12);</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1225,8 +1281,20 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (13, 'Contumil',1);</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M18" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,13);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,13);</v>
+      </c>
+      <c r="R18" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,13);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,13);</v>
+      </c>
+      <c r="W18" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,13);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,13);</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1238,7 +1306,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (14, 'Ermesinde',1);</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1250,7 +1318,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (15, 'São Frutuoso',1);</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1261,8 +1329,16 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (16, 'São Pedro da Torre',1);</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M21" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,16);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,16);</v>
+      </c>
+      <c r="R21" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,16);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,16);</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1273,8 +1349,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (17, 'Viana do Castelo',1);</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M22" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,17);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,17);</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1285,8 +1365,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (18, 'Famalicão',1);</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M23" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,18);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,18);</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1297,8 +1381,12 @@
         <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A20&amp;", '"&amp;B20&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (19, 'Barroselas',1);</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="R24" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,19);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,19);</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>50</v>
       </c>
@@ -1309,8 +1397,12 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (20, 'Nine',1);</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="W25" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,20);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,20);</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>45</v>
       </c>
@@ -1321,8 +1413,16 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (21, 'Caminha',1);</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M26" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,21);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,21);</v>
+      </c>
+      <c r="R26" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,21);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,21);</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>48</v>
       </c>
@@ -1334,7 +1434,7 @@
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (22, 'Carvalha',1);</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>43</v>
       </c>
@@ -1345,29 +1445,69 @@
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (23, 'Carreço',1);</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="W28" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,23);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,23);</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E29" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (50, 'Leixões',1);</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M29" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,50);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,50);</v>
+      </c>
+      <c r="R29" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,50);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,50);</v>
+      </c>
+      <c r="W29" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,50);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,50);</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E30" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (45, 'São Mamede de Infesta',1);</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M30" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,45);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,45);</v>
+      </c>
+      <c r="R30" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,45);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,45);</v>
+      </c>
+      <c r="W30" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,45);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,45);</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E31" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (48, 'Leça do Balio',1);</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M31" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,48);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,48);</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E32" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (43, 'São Gemil',1);</v>
+      </c>
+      <c r="M32" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,43);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,43);</v>
+      </c>
+      <c r="W32" t="str">
+        <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,43);"</f>
+        <v>INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,43);</v>
       </c>
     </row>
   </sheetData>
@@ -3591,7 +3731,7 @@
     </row>
     <row r="27" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C27" t="str">
-        <f t="shared" ref="C27:C35" si="0">"INSERT INTO Locomotive (numberLocomotive, name, yearOfEntry, operationalSpeed, model) VALUES ("&amp;A3&amp;",'"&amp;B3&amp;"',"&amp;E3&amp;","&amp;N3&amp;",1);"</f>
+        <f t="shared" ref="C27:C28" si="0">"INSERT INTO Locomotive (numberLocomotive, name, yearOfEntry, operationalSpeed, model) VALUES ("&amp;A3&amp;",'"&amp;B3&amp;"',"&amp;E3&amp;","&amp;N3&amp;",1);"</f>
         <v>INSERT INTO Locomotive (numberLocomotive, name, yearOfEntry, operationalSpeed, model) VALUES (5623,'Paz',1995,70,1);</v>
       </c>
     </row>
@@ -4256,7 +4396,7 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
-        <f t="shared" ref="B21:B29" si="1">"INSERT INTO WagonModel (id, nameModel, maker, length, width, height, maxSpeed, payload, volume, bogiesId, wagonsTypeId) VALUES ("&amp;A3&amp;",'"&amp;B3&amp;"','"&amp;C3&amp;"',"&amp;F3&amp;","&amp;G3&amp;","&amp;H3&amp;","&amp;J3&amp;","&amp;K3&amp;","&amp;L3&amp;",5,1);"</f>
+        <f t="shared" ref="B21" si="1">"INSERT INTO WagonModel (id, nameModel, maker, length, width, height, maxSpeed, payload, volume, bogiesId, wagonsTypeId) VALUES ("&amp;A3&amp;",'"&amp;B3&amp;"','"&amp;C3&amp;"',"&amp;F3&amp;","&amp;G3&amp;","&amp;H3&amp;","&amp;J3&amp;","&amp;K3&amp;","&amp;L3&amp;",5,1);"</f>
         <v>INSERT INTO WagonModel (id, nameModel, maker, length, width, height, maxSpeed, payload, volume, bogiesId, wagonsTypeId) VALUES (1278,'Tdgs 41 94 074 1','Equimetal',9640,3120,4165.5,100,26.2,38,5,1);</v>
       </c>
     </row>
@@ -4368,7 +4508,7 @@
         <v>1987</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F18" si="0">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES ("&amp;A3&amp;", 21.2,"&amp;D3&amp;",1104);"</f>
+        <f t="shared" ref="F3:F17" si="0">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES ("&amp;A3&amp;", 21.2,"&amp;D3&amp;",1104);"</f>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES (3563078, 21.2,1987,1104);</v>
       </c>
     </row>
@@ -4926,7 +5066,7 @@
         <v>2005</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" ref="F34:F44" si="4">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES ("&amp;A34&amp;",24 ,"&amp;D34&amp;",1212);"</f>
+        <f t="shared" ref="F34:F42" si="4">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES ("&amp;A34&amp;",24 ,"&amp;D34&amp;",1212);"</f>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId) VALUES (3330002,24 ,2005,1212);</v>
       </c>
     </row>

--- a/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
+++ b/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\Sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261362C4-DC27-4088-B60E-72B5A781F460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90605992-C289-45CD-A2A5-C1B4C56B831E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
@@ -1102,8 +1102,8 @@
         <v>7</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" ref="E7:E32" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A3&amp;", '"&amp;B3&amp;"',1);"</f>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (2, 'Tamel',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A3&amp;", '"&amp;B3&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (2, 'Tamel',2);</v>
       </c>
       <c r="M7" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,2);"</f>
@@ -1118,8 +1118,8 @@
         <v>8</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (3, 'Senhora das Dores',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A4&amp;", '"&amp;B4&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (3, 'Senhora das Dores',3);</v>
       </c>
       <c r="R8" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,3);"</f>
@@ -1134,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="0"/>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A5&amp;", '"&amp;B5&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (4, 'Lousado',1);</v>
       </c>
     </row>
@@ -1146,8 +1146,8 @@
         <v>10</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (5, 'Porto Campanhã',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A6&amp;", '"&amp;B6&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (5, 'Porto Campanhã',2);</v>
       </c>
       <c r="M10" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,5);"</f>
@@ -1166,8 +1166,8 @@
         <v>11</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (6, 'Leandro',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A7&amp;", '"&amp;B7&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (6, 'Leandro',3);</v>
       </c>
       <c r="W11" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,6);"</f>
@@ -1182,8 +1182,8 @@
         <v>12</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (7, 'Porto São Bento',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A8&amp;", '"&amp;B8&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (7, 'Porto São Bento',2);</v>
       </c>
       <c r="R12" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,7);"</f>
@@ -1198,8 +1198,8 @@
         <v>13</v>
       </c>
       <c r="E13" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (8, 'Barcelos',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A9&amp;", '"&amp;B9&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (8, 'Barcelos',3);</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.4">
@@ -1210,8 +1210,8 @@
         <v>14</v>
       </c>
       <c r="E14" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (9, 'Vila Nova da Cerveira',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A10&amp;", '"&amp;B10&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (9, 'Vila Nova da Cerveira',3);</v>
       </c>
       <c r="M14" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,9);"</f>
@@ -1226,7 +1226,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E15:E23" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A11&amp;", '"&amp;B11&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (10, 'Midões',1);</v>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>16</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" si="0"/>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A12&amp;", '"&amp;B12&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (11, 'Valença',1);</v>
       </c>
       <c r="M16" t="str">
@@ -1262,8 +1262,8 @@
         <v>17</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (12, 'Darque',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A13&amp;", '"&amp;B13&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (12, 'Darque',2);</v>
       </c>
       <c r="R17" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,12);"</f>
@@ -1278,8 +1278,8 @@
         <v>18</v>
       </c>
       <c r="E18" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (13, 'Contumil',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A14&amp;", '"&amp;B14&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (13, 'Contumil',3);</v>
       </c>
       <c r="M18" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,13);"</f>
@@ -1302,7 +1302,7 @@
         <v>19</v>
       </c>
       <c r="E19" t="str">
-        <f t="shared" si="0"/>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A15&amp;", '"&amp;B15&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (14, 'Ermesinde',1);</v>
       </c>
     </row>
@@ -1314,8 +1314,8 @@
         <v>20</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (15, 'São Frutuoso',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A16&amp;", '"&amp;B16&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (15, 'São Frutuoso',2);</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -1326,8 +1326,8 @@
         <v>21</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (16, 'São Pedro da Torre',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A17&amp;", '"&amp;B17&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (16, 'São Pedro da Torre',3);</v>
       </c>
       <c r="M21" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,16);"</f>
@@ -1378,8 +1378,8 @@
         <v>24</v>
       </c>
       <c r="E24" t="str">
-        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A20&amp;", '"&amp;B20&amp;"',1);"</f>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (19, 'Barroselas',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A20&amp;", '"&amp;B20&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (19, 'Barroselas',2);</v>
       </c>
       <c r="R24" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (2,19);"</f>
@@ -1394,8 +1394,8 @@
         <v>117</v>
       </c>
       <c r="E25" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (20, 'Nine',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A21&amp;", '"&amp;B21&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (20, 'Nine',2);</v>
       </c>
       <c r="W25" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (3,20);"</f>
@@ -1410,8 +1410,8 @@
         <v>140</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (21, 'Caminha',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A22&amp;", '"&amp;B22&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (21, 'Caminha',3);</v>
       </c>
       <c r="M26" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,21);"</f>
@@ -1430,8 +1430,8 @@
         <v>119</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (22, 'Carvalha',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A23&amp;", '"&amp;B23&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (22, 'Carvalha',3);</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
@@ -1442,7 +1442,7 @@
         <v>120</v>
       </c>
       <c r="E28" t="str">
-        <f t="shared" si="0"/>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A24&amp;", '"&amp;B24&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (23, 'Carreço',1);</v>
       </c>
       <c r="W28" t="str">
@@ -1452,8 +1452,8 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E29" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (50, 'Leixões',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A25&amp;", '"&amp;B25&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (50, 'Leixões',2);</v>
       </c>
       <c r="M29" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,50);"</f>
@@ -1470,8 +1470,8 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E30" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (45, 'São Mamede de Infesta',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A26&amp;", '"&amp;B26&amp;"',3);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (45, 'São Mamede de Infesta',3);</v>
       </c>
       <c r="M30" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,45);"</f>
@@ -1488,8 +1488,8 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E31" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (48, 'Leça do Balio',1);</v>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A27&amp;", '"&amp;B27&amp;"',2);"</f>
+        <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (48, 'Leça do Balio',2);</v>
       </c>
       <c r="M31" t="str">
         <f>"INSERT INTO AreaTypeStation (areaId, stationId) VALUES (1,48);"</f>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="E32" t="str">
-        <f t="shared" si="0"/>
+        <f>"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A28&amp;", '"&amp;B28&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (43, 'São Gemil',1);</v>
       </c>
       <c r="M32" t="str">
@@ -1512,6 +1512,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
+++ b/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\Sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90605992-C289-45CD-A2A5-C1B4C56B831E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656C7BBF-A9E8-49A5-903C-FDA6A70C0674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="1" activeTab="8" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -1518,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB12050A-2A4D-9940-B186-94EA523F784D}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="28.33203125" customWidth="1"/>
@@ -1689,200 +1689,201 @@
         <v>INSERT INTO OperatorTrain (operatorVatNumber, trainId) VALUES ('PT509017800',5421);</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B17" t="str">
         <f>"INSERT INTO OperatorTrain (operatorVatNumber, trainId) VALUES ('PT509017800',"&amp;A3&amp;");"</f>
         <v>INSERT INTO OperatorTrain (operatorVatNumber, trainId) VALUES ('PT509017800',5435);</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f>"INSERT INTO OperatorTrain (operatorVatNumber, trainId) VALUES ('PT509017800',"&amp;A4&amp;");"</f>
         <v>INSERT INTO OperatorTrain (operatorVatNumber, trainId) VALUES ('PT509017800',5437);</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
         <f>"INSERT INTO RouteType (id, description) VALUES (1,'simple');"</f>
         <v>INSERT INTO RouteType (id, description) VALUES (1,'simple');</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
         <f>"INSERT INTO RouteType (id, description) VALUES (2,'complex');"</f>
         <v>INSERT INTO RouteType (id, description) VALUES (2,'complex');</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,50,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,50,2,50);</v>
-      </c>
-      <c r="H23" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,11,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,11,1,11);</v>
-      </c>
-      <c r="M23" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,11,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,11,2,11);</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,50,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,50,2,50,11);</v>
+      </c>
+      <c r="I23" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,11,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,11,1,11,50);</v>
+      </c>
+      <c r="O23" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,11,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,11,2,11,50);</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,48,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,48,2,50);</v>
-      </c>
-      <c r="H24" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,16,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,16,1,11);</v>
-      </c>
-      <c r="M24" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,16,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,16,2,11);</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,48,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,48,2,50,11);</v>
+      </c>
+      <c r="I24" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,16,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,16,1,11,50);</v>
+      </c>
+      <c r="O24" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,16,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,16,2,11,50);</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,45,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,45,2,50);</v>
-      </c>
-      <c r="H25" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,21,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,21,1,11);</v>
-      </c>
-      <c r="M25" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,21,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,21,2,11);</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,45,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,45,2,50,11);</v>
+      </c>
+      <c r="I25" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,21,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,21,1,11,50);</v>
+      </c>
+      <c r="O25" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,21,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,21,2,11,50);</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,43,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,43,2,50);</v>
-      </c>
-      <c r="H26" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,17,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,17,1,11);</v>
-      </c>
-      <c r="M26" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,17,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,17,2,11);</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,43,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,43,2,50,11);</v>
+      </c>
+      <c r="I26" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,17,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,17,1,11,50);</v>
+      </c>
+      <c r="O26" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,17,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,17,2,11,50);</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B27" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,13,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,13,2,50);</v>
-      </c>
-      <c r="H27" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,12,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,12,1,11);</v>
-      </c>
-      <c r="M27" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,12,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,12,2,11);</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,13,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,13,2,50,11);</v>
+      </c>
+      <c r="I27" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,12,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,12,1,11,50);</v>
+      </c>
+      <c r="O27" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,12,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,12,2,11,50);</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B28" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,20,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,20,2,50);</v>
-      </c>
-      <c r="H28" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,8,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,8,1,11);</v>
-      </c>
-      <c r="M28" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,8,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,8,2,11);</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,20,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,20,2,50,11);</v>
+      </c>
+      <c r="I28" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,8,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,8,1,11,50);</v>
+      </c>
+      <c r="O28" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,8,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,8,2,11,50);</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B29" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,8,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,8,2,50);</v>
-      </c>
-      <c r="H29" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,20,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,20,1,11);</v>
-      </c>
-      <c r="M29" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,20,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,20,2,11);</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,8,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,8,2,50,11);</v>
+      </c>
+      <c r="I29" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,20,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,20,1,11,50);</v>
+      </c>
+      <c r="O29" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,20,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,20,2,11,50);</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B30" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,12,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,12,2,50);</v>
-      </c>
-      <c r="H30" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,13,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,13,1,11);</v>
-      </c>
-      <c r="M30" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,13,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,13,2,11);</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,12,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,12,2,50,11);</v>
+      </c>
+      <c r="I30" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,13,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,13,1,11,50);</v>
+      </c>
+      <c r="O30" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,13,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,13,2,11,50);</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B31" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,17,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,17,2,50);</v>
-      </c>
-      <c r="H31" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,43,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,43,1,11);</v>
-      </c>
-      <c r="M31" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,43,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,43,2,11);</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,17,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,17,2,50,11);</v>
+      </c>
+      <c r="I31" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,43,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,43,1,11,50);</v>
+      </c>
+      <c r="O31" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,43,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,43,2,11,50);</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B32" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,21,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,21,2,50);</v>
-      </c>
-      <c r="H32" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,45,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,45,1,11);</v>
-      </c>
-      <c r="M32" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,45,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,45,2,11);</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,21,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,21,2,50,11);</v>
+      </c>
+      <c r="I32" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,45,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,45,1,11,50);</v>
+      </c>
+      <c r="O32" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,45,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,45,2,11,50);</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B33" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,16,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,16,2,50);</v>
-      </c>
-      <c r="H33" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,48,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,48,1,11);</v>
-      </c>
-      <c r="M33" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,48,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,48,2,11);</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,16,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,16,2,50,11);</v>
+      </c>
+      <c r="I33" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,48,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,48,1,11,50);</v>
+      </c>
+      <c r="O33" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,48,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,48,2,11,50);</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B34" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,11,2,50);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5421,11,2,50);</v>
-      </c>
-      <c r="H34" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,50,1,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5435,50,1,11);</v>
-      </c>
-      <c r="M34" t="str">
-        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,50,2,11);"</f>
-        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation) VALUES (5437,50,2,11);</v>
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,11,2,50,11);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5421,11,2,50,11);</v>
+      </c>
+      <c r="I34" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,50,1,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5435,50,1,11,50);</v>
+      </c>
+      <c r="O34" t="str">
+        <f>"INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,50,2,11,50);"</f>
+        <v>INSERT INTO Route (trainId, stationId, routeTypeId, inicialStation, finalStation) VALUES (5437,50,2,11,50);</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5469,14 +5470,14 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7801BF51-1CF6-EE49-8281-CE38E390C5A0}">
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5499,7 +5500,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -5522,23 +5523,23 @@
         <v>169</v>
       </c>
       <c r="I2" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,50,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,50,50);</v>
-      </c>
-      <c r="O2" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,50,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,50,50);</v>
-      </c>
-      <c r="U2" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,20,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,20,20);</v>
-      </c>
-      <c r="AA2" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,12,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,12,12);</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,50,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,50,50,12);</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,50,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,50,50,11);</v>
+      </c>
+      <c r="Y2" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,20,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,20,20,11);</v>
+      </c>
+      <c r="AG2" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,12,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,12,12,50);</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2002</v>
       </c>
@@ -5561,23 +5562,23 @@
         <v>3563089</v>
       </c>
       <c r="I3" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,48,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,48,50);</v>
-      </c>
-      <c r="O3" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,48,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,48,50);</v>
-      </c>
-      <c r="U3" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,8,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,8,20);</v>
-      </c>
-      <c r="AA3" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,8,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,8,12);</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,48,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,48,50,12);</v>
+      </c>
+      <c r="Q3" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,48,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,48,50,11);</v>
+      </c>
+      <c r="Y3" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,8,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,8,20,11);</v>
+      </c>
+      <c r="AG3" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,8,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,8,12,50);</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2003</v>
       </c>
@@ -5600,23 +5601,23 @@
         <v>170</v>
       </c>
       <c r="I4" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,45,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,45,50);</v>
-      </c>
-      <c r="O4" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,45,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,45,50);</v>
-      </c>
-      <c r="U4" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,12,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,12,20);</v>
-      </c>
-      <c r="AA4" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,20,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,20,12);</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,45,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,45,50,12);</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,45,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,45,50,11);</v>
+      </c>
+      <c r="Y4" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,12,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,12,20,11);</v>
+      </c>
+      <c r="AG4" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,20,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,20,12,50);</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2004</v>
       </c>
@@ -5639,23 +5640,23 @@
         <v>1811013</v>
       </c>
       <c r="I5" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,43,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,43,50);</v>
-      </c>
-      <c r="O5" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,43,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,43,50);</v>
-      </c>
-      <c r="U5" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,17,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,17,20);</v>
-      </c>
-      <c r="AA5" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,13,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,13,12);</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,43,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,43,50,12);</v>
+      </c>
+      <c r="Q5" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,43,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,43,50,11);</v>
+      </c>
+      <c r="Y5" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,17,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,17,20,11);</v>
+      </c>
+      <c r="AG5" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,13,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,13,12,50);</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2005</v>
       </c>
@@ -5678,23 +5679,23 @@
         <v>171</v>
       </c>
       <c r="I6" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,13,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,13,50);</v>
-      </c>
-      <c r="O6" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,13,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,13,50);</v>
-      </c>
-      <c r="U6" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,21,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,21,20);</v>
-      </c>
-      <c r="AA6" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,43,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,43,12);</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,13,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,13,50,12);</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,13,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,13,50,11);</v>
+      </c>
+      <c r="Y6" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,21,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,21,20,11);</v>
+      </c>
+      <c r="AG6" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,43,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,43,12,50);</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2006</v>
       </c>
@@ -5717,23 +5718,23 @@
         <v>172</v>
       </c>
       <c r="I7" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,20,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,20,50);</v>
-      </c>
-      <c r="O7" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,20,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,20,50);</v>
-      </c>
-      <c r="U7" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,16,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,16,20);</v>
-      </c>
-      <c r="AA7" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,45,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,45,12);</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,20,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,20,50,12);</v>
+      </c>
+      <c r="Q7" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,20,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,20,50,11);</v>
+      </c>
+      <c r="Y7" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,16,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,16,20,11);</v>
+      </c>
+      <c r="AG7" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,45,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,45,12,50);</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2007</v>
       </c>
@@ -5756,23 +5757,23 @@
         <v>173</v>
       </c>
       <c r="I8" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,8,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,8,50);</v>
-      </c>
-      <c r="O8" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,8,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,8,50);</v>
-      </c>
-      <c r="U8" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,11,20);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2005,11,20);</v>
-      </c>
-      <c r="AA8" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,48,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,48,12);</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,8,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,8,50,12);</v>
+      </c>
+      <c r="Q8" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,8,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,8,50,11);</v>
+      </c>
+      <c r="Y8" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,11,20,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2005,11,20,11);</v>
+      </c>
+      <c r="AG8" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,48,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,48,12,50);</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2050</v>
       </c>
@@ -5795,19 +5796,19 @@
         <v>169</v>
       </c>
       <c r="I9" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,12,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2001,12,50);</v>
-      </c>
-      <c r="O9" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,12,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,12,50);</v>
-      </c>
-      <c r="AA9" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,50,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2050,50,12);</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,12,50,12);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2001,12,50,12);</v>
+      </c>
+      <c r="Q9" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,12,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,12,50,11);</v>
+      </c>
+      <c r="AG9" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,50,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2050,50,12,50);</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>2051</v>
       </c>
@@ -5829,230 +5830,230 @@
       <c r="G10" t="s">
         <v>174</v>
       </c>
-      <c r="O10" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,17,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,17,50);</v>
-      </c>
-      <c r="U10" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,12,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,12,12);</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Q10" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,17,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,17,50,11);</v>
+      </c>
+      <c r="Y10" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,12,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,12,12,50);</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="I11" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,13,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,13,13);</v>
-      </c>
-      <c r="O11" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,21,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,21,50);</v>
-      </c>
-      <c r="U11" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,8,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,8,12);</v>
-      </c>
-      <c r="AA11" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,11,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,11,11);</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,13,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,13,13,11);</v>
+      </c>
+      <c r="Q11" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,21,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,21,50,11);</v>
+      </c>
+      <c r="Y11" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,8,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,8,12,50);</v>
+      </c>
+      <c r="AG11" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,11,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,11,11,50);</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B12" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A2&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2001,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
       <c r="I12" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,20,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,20,13);</v>
-      </c>
-      <c r="O12" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,16,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,16,50);</v>
-      </c>
-      <c r="U12" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,20,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,20,12);</v>
-      </c>
-      <c r="AA12" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,16,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,16,11);</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,20,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,20,13,11);</v>
+      </c>
+      <c r="Q12" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,16,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,16,50,11);</v>
+      </c>
+      <c r="Y12" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,20,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,20,12,50);</v>
+      </c>
+      <c r="AG12" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,16,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,16,11,50);</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B13" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A3&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2002,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
       <c r="I13" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,8,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,8,13);</v>
-      </c>
-      <c r="O13" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,11,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2003,11,50);</v>
-      </c>
-      <c r="U13" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,13,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,13,12);</v>
-      </c>
-      <c r="AA13" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,21,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,21,11);</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,8,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,8,13,11);</v>
+      </c>
+      <c r="Q13" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,11,50,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2003,11,50,11);</v>
+      </c>
+      <c r="Y13" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,13,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,13,12,50);</v>
+      </c>
+      <c r="AG13" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,21,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,21,11,50);</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B14" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A4&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2003,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
       <c r="I14" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,12,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,12,13);</v>
-      </c>
-      <c r="U14" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,43,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,43,12);</v>
-      </c>
-      <c r="AA14" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,17,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,17,11);</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,12,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,12,13,11);</v>
+      </c>
+      <c r="Y14" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,43,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,43,12,50);</v>
+      </c>
+      <c r="AG14" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,17,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,17,11,50);</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B15" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A5&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2004,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
       <c r="I15" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,17,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,17,13);</v>
-      </c>
-      <c r="O15" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,50,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,50,50);</v>
-      </c>
-      <c r="U15" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,45,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,45,12);</v>
-      </c>
-      <c r="AA15" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,12,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,12,11);</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,17,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,17,13,11);</v>
+      </c>
+      <c r="Q15" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,50,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,50,50,21);</v>
+      </c>
+      <c r="Y15" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,45,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,45,12,50);</v>
+      </c>
+      <c r="AG15" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,12,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,12,11,50);</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B16" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A6&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2005,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
       <c r="I16" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,21,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,21,13);</v>
-      </c>
-      <c r="O16" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,48,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,48,50);</v>
-      </c>
-      <c r="U16" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,48,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,48,12);</v>
-      </c>
-      <c r="AA16" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,8,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,8,11);</v>
-      </c>
-    </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,21,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,21,13,11);</v>
+      </c>
+      <c r="Q16" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,48,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,48,50,21);</v>
+      </c>
+      <c r="Y16" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,48,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,48,12,50);</v>
+      </c>
+      <c r="AG16" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,8,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,8,11,50);</v>
+      </c>
+    </row>
+    <row r="17" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B17" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A7&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5435);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2006,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5435);</v>
       </c>
       <c r="I17" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,16,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,16,13);</v>
-      </c>
-      <c r="O17" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,45,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,45,50);</v>
-      </c>
-      <c r="U17" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,50,12);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2006,50,12);</v>
-      </c>
-      <c r="AA17" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,20,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,20,11);</v>
-      </c>
-    </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,16,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,16,13,11);</v>
+      </c>
+      <c r="Q17" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,45,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,45,50,21);</v>
+      </c>
+      <c r="Y17" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,50,12,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2006,50,12,50);</v>
+      </c>
+      <c r="AG17" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,20,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,20,11,50);</v>
+      </c>
+    </row>
+    <row r="18" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A9&amp;",TO_DATE('2025-10-06', 'YYYY-MM-DD'),5437);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2050,TO_DATE('2025-10-06', 'YYYY-MM-DD'),5437);</v>
       </c>
       <c r="I18" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,11,13);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2002,11,13);</v>
-      </c>
-      <c r="O18" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,43,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,43,50);</v>
-      </c>
-      <c r="AA18" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,13,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,13,11);</v>
-      </c>
-    </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.4">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,11,13,11);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2002,11,13,11);</v>
+      </c>
+      <c r="Q18" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,43,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,43,50,21);</v>
+      </c>
+      <c r="AG18" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,13,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,13,11,50);</v>
+      </c>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B19" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A10&amp;",TO_DATE('2025-10-06', 'YYYY-MM-DD'),5437);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2051,TO_DATE('2025-10-06', 'YYYY-MM-DD'),5437);</v>
       </c>
-      <c r="O19" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,13,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,13,50);</v>
-      </c>
-      <c r="U19" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,50,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,50,50);</v>
-      </c>
-      <c r="AA19" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,43,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,43,11);</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Q19" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,13,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,13,50,21);</v>
+      </c>
+      <c r="Y19" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,50,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,50,50,5);</v>
+      </c>
+      <c r="AG19" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,43,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,43,11,50);</v>
+      </c>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
         <f>"INSERT INTO Freights (id, dateFreights, trainId) VALUES ("&amp;A8&amp;",TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);"</f>
         <v>INSERT INTO Freights (id, dateFreights, trainId) VALUES (2007,TO_DATE('2025-10-03', 'YYYY-MM-DD'),5421);</v>
       </c>
-      <c r="O20" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,20,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,20,50);</v>
-      </c>
-      <c r="U20" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,48,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,48,50);</v>
-      </c>
-      <c r="AA20" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,45,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,45,11);</v>
-      </c>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="O21" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,8,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,8,50);</v>
-      </c>
-      <c r="U21" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,45,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,45,50);</v>
-      </c>
-      <c r="AA21" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,48,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,48,11);</v>
-      </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Q20" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,20,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,20,50,21);</v>
+      </c>
+      <c r="Y20" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,48,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,48,50,5);</v>
+      </c>
+      <c r="AG20" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,45,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,45,11,50);</v>
+      </c>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Q21" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,8,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,8,50,21);</v>
+      </c>
+      <c r="Y21" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,45,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,45,50,5);</v>
+      </c>
+      <c r="AG21" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,48,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,48,11,50);</v>
+      </c>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330001,2001);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330001,2001);</v>
@@ -6061,20 +6062,20 @@
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563077, 2005);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563077, 2005);</v>
       </c>
-      <c r="O22" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,12,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,12,50);</v>
-      </c>
-      <c r="U22" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,43,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,43,50);</v>
-      </c>
-      <c r="AA22" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,50,11);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2051,50,11);</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Q22" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,12,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,12,50,21);</v>
+      </c>
+      <c r="Y22" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,43,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,43,50,5);</v>
+      </c>
+      <c r="AG22" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,50,11,50);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2051,50,11,50);</v>
+      </c>
+    </row>
+    <row r="23" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330002,2001);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330002,2001);</v>
@@ -6083,16 +6084,16 @@
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563078, 2005);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563078, 2005);</v>
       </c>
-      <c r="O23" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,17,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,17,50);</v>
-      </c>
-      <c r="U23" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,13,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,13,50);</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Q23" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,17,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,17,50,21);</v>
+      </c>
+      <c r="Y23" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,13,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,13,50,5);</v>
+      </c>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330004,2001);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330004,2001);</v>
@@ -6101,16 +6102,16 @@
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563079, 2005);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563079, 2005);</v>
       </c>
-      <c r="O24" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,21,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2004,21,50);</v>
-      </c>
-      <c r="U24" t="str">
-        <f>"INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,5,50);"</f>
-        <v>INSERT INTO Path (freightsId, stationId, inicialStation) VALUES (2007,5,50);</v>
-      </c>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Q24" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,21,50,21);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2004,21,50,21);</v>
+      </c>
+      <c r="Y24" t="str">
+        <f>"INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,5,50,5);"</f>
+        <v>INSERT INTO Path (freightsId, stationId, inicialStation, finalStation) VALUES (2007,5,50,5);</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330005,2001);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330005,2001);</v>
@@ -6120,19 +6121,19 @@
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563080, 2005);</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330006,2001);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330006,2001);</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:33" x14ac:dyDescent="0.4">
       <c r="H27" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330003, 2006);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330003, 2006);</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B28" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563089,2002);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563089,2002);</v>
@@ -6142,7 +6143,7 @@
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3330007, 2006);</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B30" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (1811011, 2003);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (1811011, 2003);</v>
@@ -6152,7 +6153,7 @@
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563090, 2007);</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B31" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (1811012, 2003);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (1811012, 2003);</v>
@@ -6162,7 +6163,7 @@
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563091, 2007);</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:33" x14ac:dyDescent="0.4">
       <c r="H32" t="str">
         <f>"INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563092, 2007);"</f>
         <v>INSERT INTO WagonFreights (wagonNumber, freightsId) VALUES (3563092, 2007);</v>
@@ -6242,5 +6243,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
+++ b/sql-scripts/Sprint2/Dataset_Sprint_2_v0a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\Sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656C7BBF-A9E8-49A5-903C-FDA6A70C0674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133858DB-BA8D-4F37-B66C-6ADDFDBAB830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="1" activeTab="8" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="21930" windowHeight="13110" firstSheet="1" activeTab="9" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -2574,7 +2574,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" ref="K9:K29" si="0">"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",'','',3,"&amp;B3&amp;");"</f>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",'','',3,"&amp;B3&amp;");"</f>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (3,8000,2443,1,1,'','',3,2);</v>
       </c>
     </row>
@@ -2601,8 +2601,8 @@
         <v>2</v>
       </c>
       <c r="K10" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (10,8000,26560,1,1,'','',3,3);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A4&amp;","&amp;E4&amp;","&amp;F4&amp;",1,"&amp;C4&amp;",'','',2,"&amp;B4&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (10,8000,26560,1,1,'','',2,3);</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
@@ -2628,8 +2628,8 @@
         <v>2</v>
       </c>
       <c r="K11" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (11,8000,10000,1,2,'','',3,3);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A5&amp;","&amp;E5&amp;","&amp;F5&amp;",1,"&amp;C5&amp;",'','',2,"&amp;B5&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (11,8000,10000,1,2,'','',2,3);</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
@@ -2655,8 +2655,8 @@
         <v>1</v>
       </c>
       <c r="K12" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (15,8000,5286,1,1,'','',3,4);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A6&amp;","&amp;E6&amp;","&amp;F6&amp;",1,"&amp;C6&amp;",'','',2,"&amp;B6&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (15,8000,5286,1,1,'','',2,4);</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
@@ -2688,8 +2688,8 @@
         <v>864</v>
       </c>
       <c r="K13" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (16,8000,6000,1,2,'','',3,4);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A7&amp;","&amp;E7&amp;","&amp;F7&amp;",1,"&amp;C7&amp;",'','',2,"&amp;B7&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (16,8000,6000,1,2,'','',2,4);</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -2715,8 +2715,8 @@
         <v>1</v>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (14,8000,10387,1,1,'','',3,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A8&amp;","&amp;E8&amp;","&amp;F8&amp;",1,"&amp;C8&amp;",'','',2,"&amp;B8&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (14,8000,10387,1,1,'','',2,5);</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
@@ -2748,8 +2748,8 @@
         <v>266</v>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (12,8000,12000,1,2,'','',3,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A9&amp;","&amp;E9&amp;","&amp;F9&amp;",1,"&amp;C9&amp;",'','',2,"&amp;B9&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (12,8000,12000,1,2,'','',2,5);</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
@@ -2775,8 +2775,8 @@
         <v>1</v>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (13,8000,3100,1,3,'','',3,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A10&amp;","&amp;E10&amp;","&amp;F10&amp;",1,"&amp;C10&amp;",'','',2,"&amp;B10&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (13,8000,3100,1,3,'','',2,5);</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
@@ -2802,8 +2802,8 @@
         <v>2</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (20,6400,4890,1,1,'','',3,6);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A11&amp;","&amp;E11&amp;","&amp;F11&amp;",1,"&amp;C11&amp;",'','',2,"&amp;B11&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (20,6400,4890,1,1,'','',2,6);</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
@@ -2829,8 +2829,8 @@
         <v>2</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (18,8000,6000,1,1,'','',3,7);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A12&amp;","&amp;E12&amp;","&amp;F12&amp;",1,"&amp;C12&amp;",'','',1,"&amp;B12&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (18,8000,6000,1,1,'','',1,7);</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
@@ -2856,8 +2856,8 @@
         <v>2</v>
       </c>
       <c r="K19" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A13&amp;","&amp;E13&amp;","&amp;F13&amp;",1,"&amp;C13&amp;","&amp;H13&amp;","&amp;I13&amp;",3,"&amp;B13&amp;");"</f>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (21,8000,5000,1,2,2000,864,3,7);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A13&amp;","&amp;E13&amp;","&amp;F13&amp;",1,"&amp;C13&amp;","&amp;H13&amp;","&amp;I13&amp;",1,"&amp;B13&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (21,8000,5000,1,2,2000,864,1,7);</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
@@ -2883,8 +2883,8 @@
         <v>2</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (22,8000,12000,1,3,'','',3,7);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A14&amp;","&amp;E14&amp;","&amp;F14&amp;",1,"&amp;C14&amp;",'','',1,"&amp;B14&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (22,8000,12000,1,3,'','',1,7);</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
@@ -2910,8 +2910,8 @@
         <v>2</v>
       </c>
       <c r="K21" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A15&amp;","&amp;E15&amp;","&amp;F15&amp;",1,"&amp;C15&amp;","&amp;H15&amp;","&amp;I15&amp;",3,"&amp;B15&amp;");"</f>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (25,8000,20829,1,1,11000,266,3,8);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A15&amp;","&amp;E15&amp;","&amp;F15&amp;",1,"&amp;C15&amp;","&amp;H15&amp;","&amp;I15&amp;",1,"&amp;B15&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (25,8000,20829,1,1,11000,266,1,8);</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
@@ -2937,8 +2937,8 @@
         <v>2</v>
       </c>
       <c r="K22" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (26,8000,4264,1,1,'','',3,9);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A16&amp;","&amp;E16&amp;","&amp;F16&amp;",1,"&amp;C16&amp;",'','',1,"&amp;B16&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (26,8000,4264,1,1,'','',1,9);</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
@@ -2964,48 +2964,49 @@
         <v>2</v>
       </c>
       <c r="K23" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (30,8000,3883,1,1,'','',3,21);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A17&amp;","&amp;E17&amp;","&amp;F17&amp;",1,"&amp;C17&amp;",'','',2,"&amp;B17&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (30,8000,3883,1,1,'','',2,21);</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K24" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (31,8400,1174,1,1,'','',3,22);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A18&amp;","&amp;E18&amp;","&amp;F18&amp;",1,"&amp;C18&amp;",'','',2,"&amp;B18&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (31,8400,1174,1,1,'','',2,22);</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K25" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (32,8000,2534,1,2,'','',3,22);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A19&amp;","&amp;E19&amp;","&amp;F19&amp;",1,"&amp;C19&amp;",'','',2,"&amp;B19&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (32,8000,2534,1,2,'','',2,22);</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K26" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (33,8000,1566,1,1,'','',3,23);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A20&amp;","&amp;E20&amp;","&amp;F20&amp;",1,"&amp;C20&amp;",'','',2,"&amp;B20&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (33,8000,1566,1,1,'','',2,23);</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K27" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (34,8000,1453,1,2,'','',3,23);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A21&amp;","&amp;E21&amp;","&amp;F21&amp;",1,"&amp;C21&amp;",'','',2,"&amp;B21&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (34,8000,1453,1,2,'','',2,23);</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K28" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (35,8100,3597,1,1,'','',3,24);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A22&amp;","&amp;E22&amp;","&amp;F22&amp;",1,"&amp;C22&amp;",'','',2,"&amp;B22&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (35,8100,3597,1,1,'','',2,24);</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K29" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (36,8000,4334,1,2,'','',3,24);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES ("&amp;A23&amp;","&amp;E23&amp;","&amp;F23&amp;",1,"&amp;C23&amp;",'','',2,"&amp;B23&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmentOrder, sidingPosition, sidingLength, lineSegmentsTypeid, lineId) VALUES (36,8000,4334,1,2,'','',2,24);</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
